--- a/out/MLP-mamba2_repeat_4_000001.xlsx
+++ b/out/MLP-mamba2_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.40535882480514</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8053588248051395</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8053588248051395</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002693278016516706</v>
+        <v>-0.0002645466375784017</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1159647317513858</v>
+        <v>0.113906101317366</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2322389427117405</v>
+        <v>0.2281161879033567</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4480330870821613</v>
+        <v>0.4400786816248144</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.012636936633698</v>
+        <v>0.9946603932706923</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1378169801190144</v>
+        <v>0.1353706694220276</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.839671656870741</v>
+        <v>0.82476531032778</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02796429700280779</v>
+        <v>0.02746771580058328</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7575666496280585</v>
+        <v>0.7441176922102776</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02421796623034947</v>
+        <v>0.02378862041607782</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7780080866668823</v>
+        <v>0.7641964377267121</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01183961405481933</v>
+        <v>0.01162971663037508</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.473179781458245</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7774380936164192</v>
+        <v>0.7636365654011161</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00564840000157802</v>
+        <v>0.00554817425991194</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7768816661520727</v>
+        <v>0.7630899451830424</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002350440869065077</v>
+        <v>0.002308130893633986</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.073179781458245</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7759269883560334</v>
+        <v>0.7621522145277949</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001627085201405248</v>
+        <v>0.001598533356274281</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7768293575912367</v>
+        <v>0.7630384987096042</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006766556710369061</v>
+        <v>0.0006644142175872832</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7765530370350878</v>
+        <v>0.7627670506398133</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003484627822757088</v>
+        <v>0.0003417810661646369</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7765725965177152</v>
+        <v>0.7627861697732925</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001335641188228614</v>
+        <v>0.0001314646624770604</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7764913715251931</v>
+        <v>0.762706241010665</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.058759049633734e-05</v>
+        <v>6.944232397366555e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7764988758741251</v>
+        <v>0.7627135087978431</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.226833432442646e-05</v>
+        <v>3.170366259223818e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7764927315042421</v>
+        <v>0.762707389617218</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.258324531472877e-05</v>
+        <v>1.205041969913093e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7764855544063882</v>
+        <v>0.7627002775258331</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7764780956738501</v>
+        <v>0.7626928916847706</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7764722738683466</v>
+        <v>0.7626870698792672</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7764664090723453</v>
+        <v>0.7626812050832659</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7764607298956372</v>
+        <v>0.7626755259065576</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7764558485973878</v>
+        <v>0.7626706446083084</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.77645092739584</v>
+        <v>0.7626657234067605</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7764509194247455</v>
+        <v>0.7626657154356661</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7764510788466346</v>
+        <v>0.7626658748575551</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7764513339216574</v>
+        <v>0.762666129932578</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.776451086817729</v>
+        <v>0.7626658828286496</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7764510469622568</v>
+        <v>0.7626658429731773</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.7626658509442718</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.776451086817729</v>
+        <v>0.7626658828286496</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7764511824708628</v>
+        <v>0.7626659784817833</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7764511187021069</v>
+        <v>0.7626659147130275</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7764510788466346</v>
+        <v>0.7626658748575551</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.7626658509442718</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7764508078294231</v>
+        <v>0.7626656038403437</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7764507281184784</v>
+        <v>0.7626655241293989</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7764507759450451</v>
+        <v>0.7626655719559656</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7764508955114621</v>
+        <v>0.7626656915223826</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7764508795692732</v>
+        <v>0.7626656755801937</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7764508955114621</v>
+        <v>0.7626656915223826</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7764508795692732</v>
+        <v>0.7626656755801937</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.762665731377855</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.762665731377855</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.762665731377855</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.776451086817729</v>
+        <v>0.7626658828286496</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7764513020372796</v>
+        <v>0.7626660980482002</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7764512143552406</v>
+        <v>0.7626660103661611</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7764511665286739</v>
+        <v>0.7626659625395944</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7764512143552406</v>
+        <v>0.7626660103661611</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7764510310200679</v>
+        <v>0.7626658270309884</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7764510389911623</v>
+        <v>0.7626658350020828</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7764510469622568</v>
+        <v>0.7626658429731773</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.7626658509442718</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8053588248051395</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.7626658509442718</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.473179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7764510947888235</v>
+        <v>0.762665890799744</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7764511585575794</v>
+        <v>0.7626659545684999</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7764512701529017</v>
+        <v>0.7626660661638223</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7764513179794685</v>
+        <v>0.7626661139903891</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7764512781239962</v>
+        <v>0.7626660741349167</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7764512063841461</v>
+        <v>0.7626660023950667</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.776451325950563</v>
+        <v>0.7626661219614835</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7764511665286739</v>
+        <v>0.7626659625395944</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.762665731377855</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.473179781458245</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.7626656835512882</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.073179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7764509194247455</v>
+        <v>0.7626657154356661</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8053588248051395</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7764509034825566</v>
+        <v>0.7626656994934771</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7764507839161395</v>
+        <v>0.7626655799270601</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7764507440606673</v>
+        <v>0.7626655400715878</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.7626656835512882</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7764510230489734</v>
+        <v>0.7626658190598939</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7764510071067845</v>
+        <v>0.762665803117705</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7764509433380289</v>
+        <v>0.7626657393489494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7764508397138009</v>
+        <v>0.7626656357247215</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.473179781458245</v>
+        <v>1.414642784948225</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7764507201473838</v>
+        <v>0.7626655161583044</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7764508397138009</v>
+        <v>0.7626656357247215</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.7626656835512882</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.40535882480514</v>
+        <v>-1.443095189965484</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.7626657792044217</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.8430951899654835</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7764508636270843</v>
+        <v>0.7626656596380048</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.073179781458245</v>
+        <v>2.014642784948225</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7764508715981787</v>
+        <v>0.7626656676090993</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000001.xlsx
+++ b/out/MLP-mamba2_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.1889671851382075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540231</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239219</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239219</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239218</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002693278016516706</v>
+        <v>-0.0002123768412038917</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1159647317513858</v>
+        <v>0.09144319461647755</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2322389427117405</v>
+        <v>0.1831306419134622</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4480330870821613</v>
+        <v>0.3532934208351299</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.012636936633698</v>
+        <v>0.7985095753957692</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1378169801190144</v>
+        <v>0.1086750367099648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.839671656870741</v>
+        <v>0.6621183506351418</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02796429700280779</v>
+        <v>0.02205117990843222</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7575666496280585</v>
+        <v>0.5973746424021139</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02421796623034947</v>
+        <v>0.01909730181880294</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7780080866668823</v>
+        <v>0.6134936882552786</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01183961405481933</v>
+        <v>0.009336036558397289</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7774380936164192</v>
+        <v>0.6130440266408643</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00564840000157802</v>
+        <v>0.00445304098930724</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.5179430258540227</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7768816661520727</v>
+        <v>0.6126042185437656</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002350440869065077</v>
+        <v>0.001852185237343677</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7759269883560334</v>
+        <v>0.6118504298111757</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001627085201405248</v>
+        <v>0.001282148045363571</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7768293575912367</v>
+        <v>0.6125608590774213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006766556710369061</v>
+        <v>0.0005323353777360867</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7765530370350878</v>
+        <v>0.6123419825709674</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003484627822757088</v>
+        <v>0.0002736275618317024</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7765725965177152</v>
+        <v>0.6123563423143619</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001335641188228614</v>
+        <v>0.0001041717299816484</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7764913715251931</v>
+        <v>0.6122912558245593</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.058759049633734e-05</v>
+        <v>5.455385917893245e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7764988758741251</v>
+        <v>0.6122961178808687</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.226833432442646e-05</v>
+        <v>2.436293007379054e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7764927315042421</v>
+        <v>0.6122902145652743</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.258324531472877e-05</v>
+        <v>8.853466005543883e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7764855544063882</v>
+        <v>0.612283492512703</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>9.952340925016508e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7764780956738501</v>
+        <v>0.6122765405656179</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7764722738683466</v>
+        <v>0.6122708633340481</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7764664090723453</v>
+        <v>0.6122651908237638</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7764607298956372</v>
+        <v>0.6122596471556614</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540227</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7764558485973878</v>
+        <v>0.61225472600194</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.77645092739584</v>
+        <v>0.6122547658574122</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7764509194247455</v>
+        <v>0.6122547578863178</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7764510788466346</v>
+        <v>0.6122549173082069</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7764513339216574</v>
+        <v>0.6122551723832297</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.776451086817729</v>
+        <v>0.6122549252793014</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7764510469622568</v>
+        <v>0.6122548854238291</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.6122548933949236</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.776451086817729</v>
+        <v>0.6122549252793014</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7764511824708628</v>
+        <v>0.6122550209324351</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7764511187021069</v>
+        <v>0.6122549571636792</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7764510788466346</v>
+        <v>0.6122549173082069</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.6122548933949236</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7764508078294231</v>
+        <v>0.6122546462909955</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7764507281184784</v>
+        <v>0.6122545665800506</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7764507759450451</v>
+        <v>0.6122546144066173</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7764508955114621</v>
+        <v>0.6122547339730344</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7764508795692732</v>
+        <v>0.6122547180308455</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7764508955114621</v>
+        <v>0.6122547339730344</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7764508795692732</v>
+        <v>0.6122547180308455</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239201</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.6122547738285067</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.6122547738285067</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.6122547738285067</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.5179430258540227</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.776451086817729</v>
+        <v>0.6122549252793014</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7764513020372796</v>
+        <v>0.6122551404988519</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.7179430258540227</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7764512143552406</v>
+        <v>0.6122550528168129</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239196</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7764511665286739</v>
+        <v>0.6122550049902461</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239196</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7764512143552406</v>
+        <v>0.6122550528168129</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7764510310200679</v>
+        <v>0.6122548694816402</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7764510389911623</v>
+        <v>0.6122548774527347</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7764510469622568</v>
+        <v>0.6122548854238291</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.6122548933949236</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7764510549333512</v>
+        <v>0.6122548933949236</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.473179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7764510947888235</v>
+        <v>0.6122549332503958</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7764511585575794</v>
+        <v>0.6122549970191516</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7764512701529017</v>
+        <v>0.6122551086144741</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.059991344422392</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7764513179794685</v>
+        <v>0.6122551564410408</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.059991344422392</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7764512781239962</v>
+        <v>0.6122551165855685</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7764512063841461</v>
+        <v>0.6122550448457185</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.776451325950563</v>
+        <v>0.6122551644121352</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7764511665286739</v>
+        <v>0.6122550049902461</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776081</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7764509353669344</v>
+        <v>0.6122547738285067</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.473179781458245</v>
+        <v>0.5179430258540227</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.61225472600194</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7764509194247455</v>
+        <v>0.6122547578863178</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239207</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7764509034825566</v>
+        <v>0.6122547419441289</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7764507839161395</v>
+        <v>0.6122546223777118</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7764507440606673</v>
+        <v>0.6122545825222395</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.61225472600194</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7764510230489734</v>
+        <v>0.6122548615105458</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7764510071067845</v>
+        <v>0.6122548455683569</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7764509433380289</v>
+        <v>0.6122547817996011</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7764508397138009</v>
+        <v>0.6122546781753733</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.1400086555776079</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7764507201473838</v>
+        <v>0.6122545586089562</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7764508397138009</v>
+        <v>0.6122546781753733</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239208</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7764508875403676</v>
+        <v>0.61225472600194</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239208</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7764509831935011</v>
+        <v>0.6122548216550734</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239207</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7764508636270843</v>
+        <v>0.6122547020886566</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.073179781458245</v>
+        <v>0.3889671851382075</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7764508715981787</v>
+        <v>0.6122547100597511</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000001.xlsx
+++ b/out/MLP-mamba2_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.2221411615610123</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1889671851382075</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.8840249180793762</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1400086555776079</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3876919448375702</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.05999134442239212</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1436194628477097</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.2550621032714844</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.2210680097341537</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.2633333504199982</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3400880098342896</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1400086555776079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.6850575804710388</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1400086555776079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2311298996210098</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.05999134442239212</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.2300893366336823</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5979603370092387</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2472231537103653</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.05999134442239212</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.7233269810676575</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.7363253235816956</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.8159008026123047</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.375894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5668555498123169</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7179430258540231</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4596344828605652</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5520240664482117</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.665686309337616</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7179430258540229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3988205194473267</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2650968730449677</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2236072421073914</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.1255025863647461</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5864152312278748</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3469335436820984</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3272030651569366</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3253386318683624</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4306578636169434</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1400086555776078</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5395019054412842</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.05999134442239219</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.1057807579636574</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.05999134442239219</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4371635019779205</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5979603370092387</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.07203522324562073</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1400086555776079</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5308683514595032</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1400086555776079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.2772989869117737</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.05999134442239218</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4372994303703308</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5979603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4677607417106628</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1400086555776079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6566516160964966</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.8221443295478821</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.375894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.9596097469329834</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.375894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7710838913917542</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.375894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9908567667007446</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.375894707285654</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8429969549179077</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002123768412038917</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09144319461647755</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.92503821849823</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.375894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1831306419134622</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3532934208351299</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6605525612831116</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7179430258540228</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7985095753957692</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1086750367099648</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.007161310408264399</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.140008655577608</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6621183506351418</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02205117990843222</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.4448826313018799</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5973746424021139</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01909730181880294</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.02358819358050823</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6134936882552786</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009336036558397289</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.7469210624694824</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.140008655577608</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6130440266408643</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00445304098930724</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3123249709606171</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.5179430258540227</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6126042185437656</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001852185237343677</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.8030882477760315</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.140008655577608</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6118504298111757</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001282148045363571</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2436797171831131</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7179430258540228</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6125608590774213</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005323353777360867</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8114804625511169</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.140008655577608</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6123419825709674</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002736275618317024</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.2601664960384369</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.05999134442239201</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6123563423143619</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001041717299816484</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.2894198000431061</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6122912558245593</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.455385917893245e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4661536812782288</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6122961178808687</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.436293007379054e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.1891675442457199</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6122902145652743</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.853466005543883e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3304845988750458</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.612283492512703</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.952340925016508e-07</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.2945264577865601</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6122765405656179</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.2947612702846527</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6122708633340481</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.1570054292678833</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1400086555776081</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6122651908237638</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5824878215789795</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6122596471556614</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.7008448839187622</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7179430258540227</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.61225472600194</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4329249858856201</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6122547658574122</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9036131501197815</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.05999134442239201</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6122547578863178</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.281728059053421</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6122549173082069</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.9748470783233643</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.05999134442239201</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.1939045190811157</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.05999134442239201</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6122551723832297</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.2067790180444717</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6122549252793014</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4701785445213318</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6122548854238291</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.5861397981643677</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3212908208370209</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6122548933949236</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3024603724479675</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.9674709439277649</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6122549252793014</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.2900263667106628</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6122550209324351</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.171035572886467</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6122549571636792</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.236937090754509</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6122549173082069</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.09484270215034485</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6122548933949236</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2328857481479645</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6122546462909955</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5611900091171265</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6122545665800506</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.6924205422401428</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6122546144066173</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2317729890346527</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6122547339730344</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5376347899436951</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.05999134442239201</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6122547180308455</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4068954885005951</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6122547339730344</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.7020384669303894</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.05999134442239201</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6122547180308455</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3924998939037323</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.05999134442239201</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6122547738285067</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.283092737197876</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.140008655577608</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6122547738285067</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9424011707305908</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6122547738285067</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.438801109790802</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5179430258540227</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6122549252793014</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.8181784749031067</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6122551404988519</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2358078062534332</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7179430258540227</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6122550528168129</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.6615589261054993</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.05999134442239196</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6122550049902461</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.08275248855352402</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.05999134442239196</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6122550528168129</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3886495232582092</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6122548694816402</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.288452535867691</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6122548774527347</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7169147133827209</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6122548854238291</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2399871349334717</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6122548933949236</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4456000030040741</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1400086555776081</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6122548933949236</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.8622359037399292</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6122549332503958</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.7582150101661682</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.375894707285654</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6122549970191516</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6445869207382202</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6122551086144741</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2530388832092285</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.059991344422392</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6122551564410408</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3402752280235291</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.059991344422392</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6122551165855685</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.7633954882621765</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6122550448457185</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1168889552354813</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6122551644121352</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.1329919695854187</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6122550049902461</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2973344922065735</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1400086555776081</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6122547738285067</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.506113588809967</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5179430258540227</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.61225472600194</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5119106769561768</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6122547578863178</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4603020846843719</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.05999134442239207</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.1440848708152771</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1733533442020416</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6122547419441289</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.1983072012662888</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.140008655577608</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6122546223777118</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7897731065750122</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6122545825222395</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.7058926224708557</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.375894707285654</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.61225472600194</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.5367333889007568</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6122548615105458</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.1346181035041809</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.05999134442239212</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6122548455683569</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.274109959602356</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.1907099783420563</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6122547817996011</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.110908217728138</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1400086555776079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6122546781753733</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.90984708070755</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1400086555776079</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6122545586089562</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4023813307285309</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6122546781753733</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.7464228868484497</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.05999134442239208</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.61225472600194</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.1505039781332016</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.05999134442239208</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6122548216550734</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4143879115581512</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.05999134442239207</v>
+        <v>0.01999999999999985</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6122547020886566</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6152881383895874</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3889671851382075</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6122547100597511</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_4_000001.xlsx
+++ b/out/MLP-mamba2_repeat_4_000001.xlsx
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.1436194628477097</v>
+        <v>0.143619492650032</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.2210680097341537</v>
+        <v>0.2210680395364761</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.3400880098342896</v>
+        <v>0.3400880396366119</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2311298996210098</v>
+        <v>0.2311298698186874</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.2300893366336823</v>
+        <v>0.2300893068313599</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.5668555498123169</v>
+        <v>0.5668554902076721</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4596344828605652</v>
+        <v>0.4596344530582428</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.5520240664482117</v>
+        <v>0.5520241260528564</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3988205194473267</v>
+        <v>0.3988204598426819</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2650968730449677</v>
+        <v>0.26509690284729</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3469335436820984</v>
+        <v>0.3469335734844208</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3272030651569366</v>
+        <v>0.327203094959259</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3253386318683624</v>
+        <v>0.3253386616706848</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.4306578636169434</v>
+        <v>0.430657833814621</v>
       </c>
       <c r="JB29" t="n">
         <v>0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.5395019054412842</v>
+        <v>0.539501965045929</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4371635019779205</v>
+        <v>0.4371635317802429</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.07203522324562073</v>
+        <v>0.07203523814678192</v>
       </c>
       <c r="JB33" t="n">
         <v>0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.4677607417106628</v>
+        <v>0.4677607119083405</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.6566516160964966</v>
+        <v>0.6566515564918518</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.6605525612831116</v>
+        <v>0.6605525016784668</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.007161310408264399</v>
+        <v>0.007161307148635387</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.4448826313018799</v>
+        <v>0.4448825716972351</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.8030882477760315</v>
+        <v>0.803088366985321</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2436797171831131</v>
+        <v>0.2436796575784683</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.8114804625511169</v>
+        <v>0.8114803433418274</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1600000000000001</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.2601664960384369</v>
+        <v>0.2601666748523712</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4661536812782288</v>
+        <v>0.466153621673584</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1891675442457199</v>
+        <v>0.1891675144433975</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3304845988750458</v>
+        <v>0.3304846286773682</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.2945264577865601</v>
+        <v>0.2945264279842377</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.2947612702846527</v>
+        <v>0.2947612404823303</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.1570054292678833</v>
+        <v>0.1570053547620773</v>
       </c>
       <c r="JB61" t="n">
         <v>0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.7008448839187622</v>
+        <v>0.7008448243141174</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.4329249858856201</v>
+        <v>0.4329250156879425</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.1939045190811157</v>
+        <v>0.1939045041799545</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.3024603724479675</v>
+        <v>0.3024604022502899</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.236937090754509</v>
+        <v>0.2369370311498642</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.09484270215034485</v>
+        <v>0.09484265744686127</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2328857481479645</v>
+        <v>0.2328857779502869</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2317729890346527</v>
+        <v>0.2317730188369751</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5376347899436951</v>
+        <v>0.5376347303390503</v>
       </c>
       <c r="JB83" t="n">
         <v>0.5799999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.7020384669303894</v>
+        <v>0.7020384073257446</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.438801109790802</v>
+        <v>0.4388010501861572</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3886495232582092</v>
+        <v>0.3886494636535645</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.288452535867691</v>
+        <v>0.2884525656700134</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.7169147133827209</v>
+        <v>0.7169146537780762</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4456000030040741</v>
+        <v>0.4455999433994293</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.2530388832092285</v>
+        <v>0.2530389130115509</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3402752280235291</v>
+        <v>0.3402751684188843</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1329919695854187</v>
+        <v>0.1329919844865799</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4603020846843719</v>
+        <v>0.4603021442890167</v>
       </c>
       <c r="JB110" t="n">
         <v>0.16</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.1440848708152771</v>
+        <v>0.1440848559141159</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.1199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1733533442020416</v>
+        <v>0.173353374004364</v>
       </c>
       <c r="JB112" t="n">
         <v>0.02000000000000007</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.1346181035041809</v>
+        <v>0.1346181333065033</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.274109959602356</v>
+        <v>0.2741099298000336</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.1907099783420563</v>
+        <v>0.1907100081443787</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4143879115581512</v>
+        <v>0.414387971162796</v>
       </c>
       <c r="JB125" t="n">
         <v>0.01999999999999985</v>
